--- a/data/fires-extra-codes.xlsx
+++ b/data/fires-extra-codes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10411"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/david/Box Sync/Civio/Proyectos/23 España en llamas/01 Datos/03 Códigos complementarios/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/31d2c3465a38c4b4/UNIVERSIDAD/3ER_CURSO/PRIMER_CUATRI/ADQ_DATOS/PRACTICAS/PROYECTO/Proyecto-Incendios-APD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{448C2040-36C9-3645-AB93-A67172BF0D5B}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{448C2040-36C9-3645-AB93-A67172BF0D5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7160" yWindow="940" windowWidth="35840" windowHeight="21900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="regions" sheetId="4" r:id="rId1"/>
@@ -485,7 +485,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -791,16 +791,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3ACF238-EB0D-1B46-9B8B-A72EB70BF609}">
   <dimension ref="A1:E53"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.796875" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" style="1"/>
-    <col min="2" max="2" width="24.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" style="1"/>
-    <col min="4" max="4" width="19.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="1" width="10.796875" style="1"/>
+    <col min="2" max="2" width="24.1328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.796875" style="1"/>
+    <col min="4" max="4" width="19.796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="10.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
         <v>138</v>
       </c>
@@ -817,7 +817,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -831,7 +831,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -845,7 +845,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -859,7 +859,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -873,7 +873,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -887,7 +887,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -901,7 +901,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -915,7 +915,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -929,7 +929,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A10" s="1">
         <v>2</v>
       </c>
@@ -943,7 +943,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A11" s="1">
         <v>2</v>
       </c>
@@ -957,7 +957,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -971,7 +971,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A13" s="1">
         <v>3</v>
       </c>
@@ -985,7 +985,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A14" s="1">
         <v>4</v>
       </c>
@@ -999,7 +999,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A15" s="1">
         <v>5</v>
       </c>
@@ -1013,7 +1013,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A16" s="1">
         <v>5</v>
       </c>
@@ -1027,7 +1027,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A17" s="1">
         <v>6</v>
       </c>
@@ -1041,7 +1041,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A18" s="1">
         <v>7</v>
       </c>
@@ -1055,7 +1055,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A19" s="1">
         <v>7</v>
       </c>
@@ -1069,7 +1069,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A20" s="1">
         <v>7</v>
       </c>
@@ -1083,7 +1083,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A21" s="1">
         <v>7</v>
       </c>
@@ -1097,7 +1097,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A22" s="1">
         <v>7</v>
       </c>
@@ -1111,7 +1111,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A23" s="1">
         <v>7</v>
       </c>
@@ -1125,7 +1125,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A24" s="1">
         <v>7</v>
       </c>
@@ -1139,7 +1139,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A25" s="1">
         <v>7</v>
       </c>
@@ -1153,7 +1153,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A26" s="1">
         <v>7</v>
       </c>
@@ -1167,7 +1167,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A27" s="1">
         <v>8</v>
       </c>
@@ -1181,7 +1181,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A28" s="1">
         <v>8</v>
       </c>
@@ -1195,7 +1195,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A29" s="1">
         <v>8</v>
       </c>
@@ -1209,7 +1209,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A30" s="1">
         <v>8</v>
       </c>
@@ -1223,7 +1223,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A31" s="1">
         <v>8</v>
       </c>
@@ -1237,7 +1237,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A32" s="1">
         <v>9</v>
       </c>
@@ -1251,7 +1251,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A33" s="1">
         <v>9</v>
       </c>
@@ -1265,7 +1265,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A34" s="1">
         <v>9</v>
       </c>
@@ -1279,7 +1279,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A35" s="1">
         <v>9</v>
       </c>
@@ -1293,7 +1293,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A36" s="1">
         <v>10</v>
       </c>
@@ -1307,7 +1307,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A37" s="1">
         <v>10</v>
       </c>
@@ -1321,7 +1321,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A38" s="1">
         <v>10</v>
       </c>
@@ -1335,7 +1335,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A39" s="1">
         <v>11</v>
       </c>
@@ -1349,7 +1349,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A40" s="1">
         <v>11</v>
       </c>
@@ -1363,7 +1363,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A41" s="1">
         <v>12</v>
       </c>
@@ -1377,7 +1377,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A42" s="1">
         <v>12</v>
       </c>
@@ -1391,7 +1391,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A43" s="1">
         <v>12</v>
       </c>
@@ -1405,7 +1405,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A44" s="1">
         <v>12</v>
       </c>
@@ -1419,7 +1419,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A45" s="1">
         <v>13</v>
       </c>
@@ -1433,7 +1433,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A46" s="1">
         <v>14</v>
       </c>
@@ -1447,7 +1447,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A47" s="1">
         <v>15</v>
       </c>
@@ -1461,7 +1461,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A48" s="1">
         <v>16</v>
       </c>
@@ -1475,7 +1475,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A49" s="1">
         <v>16</v>
       </c>
@@ -1489,7 +1489,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A50" s="1">
         <v>16</v>
       </c>
@@ -1503,7 +1503,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A51" s="1">
         <v>17</v>
       </c>
@@ -1517,7 +1517,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A52" s="1">
         <v>18</v>
       </c>
@@ -1531,7 +1531,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A53" s="1">
         <v>19</v>
       </c>
@@ -1555,13 +1555,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="29.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -1572,7 +1572,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1583,7 +1583,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1594,7 +1594,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1605,7 +1605,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1616,7 +1616,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -1627,7 +1627,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -1647,14 +1647,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29EC34F0-BD6A-CB41-83EE-9E1B27AAC490}">
   <dimension ref="A1:B60"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>280</v>
       </c>
@@ -1662,7 +1662,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>281</v>
       </c>
@@ -1670,7 +1670,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>282</v>
       </c>
@@ -1678,7 +1678,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>283</v>
       </c>
@@ -1686,7 +1686,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>284</v>
       </c>
@@ -1694,7 +1694,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>291</v>
       </c>
@@ -1702,7 +1702,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>292</v>
       </c>
@@ -1710,7 +1710,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>293</v>
       </c>
@@ -1718,7 +1718,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>294</v>
       </c>
@@ -1726,7 +1726,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>295</v>
       </c>
@@ -1734,7 +1734,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A12">
         <v>270</v>
       </c>
@@ -1742,7 +1742,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>260</v>
       </c>
@@ -1750,7 +1750,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A14">
         <v>250</v>
       </c>
@@ -1758,7 +1758,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>210</v>
       </c>
@@ -1766,7 +1766,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A16">
         <v>211</v>
       </c>
@@ -1774,7 +1774,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A17">
         <v>212</v>
       </c>
@@ -1782,7 +1782,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A18">
         <v>213</v>
       </c>
@@ -1790,7 +1790,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A19">
         <v>214</v>
       </c>
@@ -1798,7 +1798,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A20">
         <v>215</v>
       </c>
@@ -1806,7 +1806,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A21">
         <v>220</v>
       </c>
@@ -1814,7 +1814,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A22">
         <v>240</v>
       </c>
@@ -1822,7 +1822,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A23">
         <v>230</v>
       </c>
@@ -1830,7 +1830,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>223</v>
       </c>
@@ -1838,7 +1838,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>222</v>
       </c>
@@ -1846,7 +1846,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A26">
         <v>221</v>
       </c>
@@ -1854,7 +1854,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A27">
         <v>340</v>
       </c>
@@ -1862,7 +1862,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A28">
         <v>335</v>
       </c>
@@ -1870,7 +1870,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A29">
         <v>334</v>
       </c>
@@ -1878,7 +1878,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A30">
         <v>333</v>
       </c>
@@ -1886,7 +1886,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A31">
         <v>332</v>
       </c>
@@ -1894,7 +1894,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A32">
         <v>331</v>
       </c>
@@ -1902,7 +1902,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A33">
         <v>330</v>
       </c>
@@ -1910,7 +1910,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A34">
         <v>320</v>
       </c>
@@ -1918,7 +1918,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A35">
         <v>310</v>
       </c>
@@ -1926,12 +1926,12 @@
         <v>44</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A38">
         <v>41</v>
       </c>
@@ -1939,7 +1939,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A39">
         <v>42</v>
       </c>
@@ -1947,7 +1947,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A40">
         <v>43</v>
       </c>
@@ -1955,7 +1955,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A41">
         <v>44</v>
       </c>
@@ -1963,7 +1963,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A42">
         <v>45</v>
       </c>
@@ -1971,7 +1971,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A43">
         <v>46</v>
       </c>
@@ -1979,7 +1979,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A44">
         <v>47</v>
       </c>
@@ -1987,7 +1987,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A45">
         <v>48</v>
       </c>
@@ -1995,7 +1995,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A46">
         <v>49</v>
       </c>
@@ -2003,7 +2003,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A47">
         <v>410</v>
       </c>
@@ -2011,7 +2011,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A48">
         <v>411</v>
       </c>
@@ -2019,7 +2019,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A49">
         <v>412</v>
       </c>
@@ -2027,7 +2027,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A50">
         <v>413</v>
       </c>
@@ -2035,7 +2035,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A51">
         <v>414</v>
       </c>
@@ -2043,7 +2043,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A52">
         <v>415</v>
       </c>
@@ -2051,7 +2051,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A53">
         <v>416</v>
       </c>
@@ -2059,7 +2059,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A54">
         <v>417</v>
       </c>
@@ -2067,7 +2067,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A55">
         <v>418</v>
       </c>
@@ -2075,7 +2075,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A56">
         <v>419</v>
       </c>
@@ -2083,7 +2083,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A57">
         <v>420</v>
       </c>
@@ -2091,7 +2091,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A58">
         <v>421</v>
       </c>
@@ -2099,7 +2099,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A59">
         <v>422</v>
       </c>
@@ -2107,7 +2107,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A60">
         <v>423</v>
       </c>
